--- a/docs/design/stat_rework_roster.xlsx
+++ b/docs/design/stat_rework_roster.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="137">
   <si>
     <t xml:space="preserve">Race attributes — hand-authored (COMBAT_SPEC section 12, step 1)</t>
   </si>
@@ -188,6 +188,9 @@
     <t xml:space="preserve">Versatile</t>
   </si>
   <si>
+    <t xml:space="preserve">Ghoul</t>
+  </si>
+  <si>
     <t xml:space="preserve">Creatures &amp; villains — same nine attributes (COMBAT_SPEC amendment 2026-08-06, note 4)</t>
   </si>
   <si>
@@ -380,7 +383,7 @@
     <t xml:space="preserve">Attributes</t>
   </si>
   <si>
-    <t xml:space="preserve">153 hand-authored values: 9 attributes x 17 races. Step 1 of COMBAT_SPEC section 12.</t>
+    <t xml:space="preserve">162 hand-authored values: 9 attributes x 18 races (the Ghoul added 2026-09-27, LIVING_WORLD L3). Step 1 of COMBAT_SPEC section 12.</t>
   </si>
   <si>
     <t xml:space="preserve">Skill templates</t>
@@ -598,24 +601,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -623,7 +630,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -639,7 +646,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -655,11 +662,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -675,7 +682,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -934,1121 +941,1174 @@
   <dimension ref="A1:S31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="5" style="0" width="7.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="5" style="1" width="7.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" s="4" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="S2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" s="8" t="n">
+      <c r="E5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="9" t="n">
         <f aca="false">8+H5*2</f>
         <v>18</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" s="10" t="n">
         <f aca="false">1+(G5-5)/$R$2</f>
         <v>1</v>
       </c>
-      <c r="P5" s="8" t="str">
+      <c r="P5" s="9" t="str">
         <f aca="false">IF(AND(E5&gt;=F5,E5&gt;=I5),"Melee",IF(F5&gt;=I5,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="11" t="n">
+      <c r="E6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="13" t="n">
         <f aca="false">8+H6*2</f>
         <v>16</v>
       </c>
-      <c r="O6" s="13" t="n">
+      <c r="O6" s="14" t="n">
         <f aca="false">1+(G6-5)/$R$2</f>
         <v>0.9</v>
       </c>
-      <c r="P6" s="12" t="str">
+      <c r="P6" s="13" t="str">
         <f aca="false">IF(AND(E6&gt;=F6,E6&gt;=I6),"Melee",IF(F6&gt;=I6,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="11" t="n">
+      <c r="F7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N7" s="12" t="n">
+      <c r="I7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="13" t="n">
         <f aca="false">8+H7*2</f>
         <v>22</v>
       </c>
-      <c r="O7" s="13" t="n">
+      <c r="O7" s="14" t="n">
         <f aca="false">1+(G7-5)/$R$2</f>
         <v>1</v>
       </c>
-      <c r="P7" s="12" t="str">
+      <c r="P7" s="13" t="str">
         <f aca="false">IF(AND(E7&gt;=F7,E7&gt;=I7),"Melee",IF(F7&gt;=I7,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" s="11" t="n">
+      <c r="E8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M8" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" s="12" t="n">
+      <c r="M8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" s="13" t="n">
         <f aca="false">8+H8*2</f>
         <v>20</v>
       </c>
-      <c r="O8" s="13" t="n">
+      <c r="O8" s="14" t="n">
         <f aca="false">1+(G8-5)/$R$2</f>
         <v>1</v>
       </c>
-      <c r="P8" s="12" t="str">
+      <c r="P8" s="13" t="str">
         <f aca="false">IF(AND(E8&gt;=F8,E8&gt;=I8),"Melee",IF(F8&gt;=I8,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="11" t="n">
+      <c r="F9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N9" s="12" t="n">
+      <c r="I9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" s="13" t="n">
         <f aca="false">8+H9*2</f>
         <v>24</v>
       </c>
-      <c r="O9" s="13" t="n">
+      <c r="O9" s="14" t="n">
         <f aca="false">1+(G9-5)/$R$2</f>
         <v>0.8</v>
       </c>
-      <c r="P9" s="12" t="str">
+      <c r="P9" s="13" t="str">
         <f aca="false">IF(AND(E9&gt;=F9,E9&gt;=I9),"Melee",IF(F9&gt;=I9,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="11" t="n">
+      <c r="F10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" s="12" t="n">
+      <c r="I10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="13" t="n">
         <f aca="false">8+H10*2</f>
         <v>26</v>
       </c>
-      <c r="O10" s="13" t="n">
+      <c r="O10" s="14" t="n">
         <f aca="false">1+(G10-5)/$R$2</f>
         <v>0.9</v>
       </c>
-      <c r="P10" s="12" t="str">
+      <c r="P10" s="13" t="str">
         <f aca="false">IF(AND(E10&gt;=F10,E10&gt;=I10),"Melee",IF(F10&gt;=I10,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="11" t="n">
+      <c r="E11" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="N11" s="12" t="n">
+      <c r="I11" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" s="13" t="n">
         <f aca="false">8+H11*2</f>
         <v>22</v>
       </c>
-      <c r="O11" s="13" t="n">
+      <c r="O11" s="14" t="n">
         <f aca="false">1+(G11-5)/$R$2</f>
         <v>0.9</v>
       </c>
-      <c r="P11" s="12" t="str">
+      <c r="P11" s="13" t="str">
         <f aca="false">IF(AND(E11&gt;=F11,E11&gt;=I11),"Melee",IF(F11&gt;=I11,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N12" s="12" t="n">
+      <c r="E12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" s="13" t="n">
         <f aca="false">8+H12*2</f>
         <v>14</v>
       </c>
-      <c r="O12" s="13" t="n">
+      <c r="O12" s="14" t="n">
         <f aca="false">1+(G12-5)/$R$2</f>
         <v>1.1</v>
       </c>
-      <c r="P12" s="12" t="str">
+      <c r="P12" s="13" t="str">
         <f aca="false">IF(AND(E12&gt;=F12,E12&gt;=I12),"Melee",IF(F12&gt;=I12,"Ranged","Arcane"))</f>
         <v>Ranged</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" s="11" t="n">
+      <c r="F13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I13" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M13" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N13" s="12" t="n">
+      <c r="I13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" s="13" t="n">
         <f aca="false">8+H13*2</f>
         <v>24</v>
       </c>
-      <c r="O13" s="13" t="n">
+      <c r="O13" s="14" t="n">
         <f aca="false">1+(G13-5)/$R$2</f>
         <v>1.1</v>
       </c>
-      <c r="P13" s="12" t="str">
+      <c r="P13" s="13" t="str">
         <f aca="false">IF(AND(E13&gt;=F13,E13&gt;=I13),"Melee",IF(F13&gt;=I13,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="11" t="n">
+      <c r="E14" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" s="11" t="n">
+      <c r="I14" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="N14" s="13" t="n">
         <f aca="false">8+H14*2</f>
         <v>22</v>
       </c>
-      <c r="O14" s="13" t="n">
+      <c r="O14" s="14" t="n">
         <f aca="false">1+(G14-5)/$R$2</f>
         <v>0.9</v>
       </c>
-      <c r="P14" s="12" t="str">
+      <c r="P14" s="13" t="str">
         <f aca="false">IF(AND(E14&gt;=F14,E14&gt;=I14),"Melee",IF(F14&gt;=I14,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="11" t="n">
+      <c r="E15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J15" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" s="12" t="n">
+      <c r="J15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" s="13" t="n">
         <f aca="false">8+H15*2</f>
         <v>14</v>
       </c>
-      <c r="O15" s="13" t="n">
+      <c r="O15" s="14" t="n">
         <f aca="false">1+(G15-5)/$R$2</f>
         <v>0.9</v>
       </c>
-      <c r="P15" s="12" t="str">
+      <c r="P15" s="13" t="str">
         <f aca="false">IF(AND(E15&gt;=F15,E15&gt;=I15),"Melee",IF(F15&gt;=I15,"Ranged","Arcane"))</f>
         <v>Arcane</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="11" t="n">
+      <c r="E16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="11" t="n">
+      <c r="G16" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L16" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M16" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" s="12" t="n">
+      <c r="L16" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" s="13" t="n">
         <f aca="false">8+H16*2</f>
         <v>16</v>
       </c>
-      <c r="O16" s="13" t="n">
+      <c r="O16" s="14" t="n">
         <f aca="false">1+(G16-5)/$R$2</f>
         <v>1.1</v>
       </c>
-      <c r="P16" s="12" t="str">
+      <c r="P16" s="13" t="str">
         <f aca="false">IF(AND(E16&gt;=F16,E16&gt;=I16),"Melee",IF(F16&gt;=I16,"Ranged","Arcane"))</f>
         <v>Ranged</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="11" t="n">
+      <c r="E17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="11" t="n">
+      <c r="J17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L17" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N17" s="12" t="n">
+      <c r="L17" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" s="13" t="n">
         <f aca="false">8+H17*2</f>
         <v>16</v>
       </c>
-      <c r="O17" s="13" t="n">
+      <c r="O17" s="14" t="n">
         <f aca="false">1+(G17-5)/$R$2</f>
         <v>1.1</v>
       </c>
-      <c r="P17" s="12" t="str">
+      <c r="P17" s="13" t="str">
         <f aca="false">IF(AND(E17&gt;=F17,E17&gt;=I17),"Melee",IF(F17&gt;=I17,"Ranged","Arcane"))</f>
         <v>Arcane</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" s="11" t="n">
+      <c r="E18" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L18" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="12" t="n">
+      <c r="H18" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="13" t="n">
         <f aca="false">8+H18*2</f>
         <v>14</v>
       </c>
-      <c r="O18" s="13" t="n">
+      <c r="O18" s="14" t="n">
         <f aca="false">1+(G18-5)/$R$2</f>
         <v>1.2</v>
       </c>
-      <c r="P18" s="12" t="str">
+      <c r="P18" s="13" t="str">
         <f aca="false">IF(AND(E18&gt;=F18,E18&gt;=I18),"Melee",IF(F18&gt;=I18,"Ranged","Arcane"))</f>
         <v>Ranged</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" s="11" t="n">
+      <c r="E19" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H19" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" s="11" t="n">
+      <c r="H19" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N19" s="12" t="n">
+      <c r="L19" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" s="13" t="n">
         <f aca="false">8+H19*2</f>
         <v>18</v>
       </c>
-      <c r="O19" s="13" t="n">
+      <c r="O19" s="14" t="n">
         <f aca="false">1+(G19-5)/$R$2</f>
         <v>1.2</v>
       </c>
-      <c r="P19" s="12" t="str">
+      <c r="P19" s="13" t="str">
         <f aca="false">IF(AND(E19&gt;=F19,E19&gt;=I19),"Melee",IF(F19&gt;=I19,"Ranged","Arcane"))</f>
         <v>Ranged</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="11" t="n">
+      <c r="E20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L20" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M20" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="N20" s="12" t="n">
+      <c r="L20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N20" s="13" t="n">
         <f aca="false">8+H20*2</f>
         <v>16</v>
       </c>
-      <c r="O20" s="13" t="n">
+      <c r="O20" s="14" t="n">
         <f aca="false">1+(G20-5)/$R$2</f>
         <v>1</v>
       </c>
-      <c r="P20" s="12" t="str">
+      <c r="P20" s="13" t="str">
         <f aca="false">IF(AND(E20&gt;=F20,E20&gt;=I20),"Melee",IF(F20&gt;=I20,"Ranged","Arcane"))</f>
         <v>Ranged</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" s="12" t="n">
+      <c r="E21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" s="13" t="n">
         <f aca="false">8+H21*2</f>
         <v>18</v>
       </c>
-      <c r="O21" s="13" t="n">
+      <c r="O21" s="14" t="n">
         <f aca="false">1+(G21-5)/$R$2</f>
         <v>1</v>
       </c>
-      <c r="P21" s="12" t="str">
+      <c r="P21" s="13" t="str">
         <f aca="false">IF(AND(E21&gt;=F21,E21&gt;=I21),"Melee",IF(F21&gt;=I21,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="B22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <f aca="false">8+H22*2</f>
+        <v>20</v>
+      </c>
+      <c r="O22" s="14" t="n">
+        <f aca="false">1+(G22-5)/$R$2</f>
+        <v>1.1</v>
+      </c>
+      <c r="P22" s="13" t="str">
+        <f aca="false">IF(AND(E22&gt;=F22,E22&gt;=I22),"Melee",IF(F22&gt;=I22,"Ranged","Arcane"))</f>
+        <v>Melee</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="14" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="B24" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I24" s="15" t="n">
+      <c r="D24" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="J24" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="L24" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" s="14" t="s">
+      <c r="J24" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="N24" s="14" t="n">
+      <c r="N24" s="15" t="n">
         <f aca="false">8+H24*2</f>
         <v>20</v>
       </c>
-      <c r="O24" s="14" t="n">
+      <c r="O24" s="15" t="n">
         <f aca="false">1+(G24-5)/$R$2</f>
         <v>1</v>
       </c>
-      <c r="P24" s="14" t="str">
+      <c r="P24" s="15" t="str">
         <f aca="false">IF(AND(E24&gt;=F24,E24&gt;=I24),"Melee",IF(F24&gt;=I24,"Ranged","Arcane"))</f>
         <v>Arcane</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="14" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="B25" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" s="15" t="n">
+      <c r="D25" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="H25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="N25" s="14" t="n">
+      <c r="H25" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" s="15" t="n">
         <f aca="false">8+H25*2</f>
         <v>18</v>
       </c>
-      <c r="O25" s="14" t="n">
+      <c r="O25" s="15" t="n">
         <f aca="false">1+(G25-5)/$R$2</f>
         <v>1.3</v>
       </c>
-      <c r="P25" s="14" t="str">
+      <c r="P25" s="15" t="str">
         <f aca="false">IF(AND(E25&gt;=F25,E25&gt;=I25),"Melee",IF(F25&gt;=I25,"Ranged","Arcane"))</f>
         <v>Melee</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2070,350 +2130,350 @@
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="5" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="J4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="M4" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="B5" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="11" t="n">
+      <c r="B6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="11" t="n">
+      <c r="D7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" s="11" t="n">
+      <c r="F8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="L9" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="B10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="16" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="M14" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2436,985 +2496,1041 @@
   <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="5" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="K4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="N4" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="17" t="n">
+      <c r="B5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="18" t="n">
         <f aca="false">'Skill templates'!B10</f>
         <v>5</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">'Skill templates'!C10</f>
         <v>5</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">'Skill templates'!D10</f>
         <v>5</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <f aca="false">'Skill templates'!E10</f>
         <v>5</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <f aca="false">'Skill templates'!F10</f>
         <v>5</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="18" t="n">
         <f aca="false">'Skill templates'!G10</f>
         <v>5</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <f aca="false">'Skill templates'!H10</f>
         <v>5</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="18" t="n">
         <f aca="false">'Skill templates'!I10</f>
         <v>5</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="K5" s="18" t="n">
         <f aca="false">'Skill templates'!J10</f>
         <v>5</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="18" t="n">
         <f aca="false">'Skill templates'!K10</f>
         <v>5</v>
       </c>
-      <c r="M5" s="17" t="n">
+      <c r="M5" s="18" t="n">
         <f aca="false">'Skill templates'!L10</f>
         <v>5</v>
       </c>
-      <c r="N5" s="17" t="n">
+      <c r="N5" s="18" t="n">
         <f aca="false">'Skill templates'!M10</f>
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="17" t="n">
+      <c r="B6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="18" t="n">
         <f aca="false">'Skill templates'!B5</f>
         <v>3</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <f aca="false">'Skill templates'!C5</f>
         <v>3</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <f aca="false">'Skill templates'!D5</f>
         <v>2</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <f aca="false">'Skill templates'!E5</f>
         <v>1</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <f aca="false">'Skill templates'!F5</f>
         <v>1</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <f aca="false">'Skill templates'!G5</f>
         <v>1</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <f aca="false">'Skill templates'!H5</f>
         <v>1</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="18" t="n">
         <f aca="false">'Skill templates'!I5</f>
         <v>1</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="18" t="n">
         <f aca="false">'Skill templates'!J5</f>
         <v>1</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="18" t="n">
         <f aca="false">'Skill templates'!K5</f>
         <v>1</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="18" t="n">
         <f aca="false">'Skill templates'!L5</f>
         <v>1</v>
       </c>
-      <c r="N6" s="17" t="n">
+      <c r="N6" s="18" t="n">
         <f aca="false">'Skill templates'!M5</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="17" t="n">
+      <c r="B7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="18" t="n">
         <f aca="false">'Skill templates'!B6</f>
         <v>5</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">'Skill templates'!C6</f>
         <v>4</v>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="17" t="n">
+      <c r="E7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <f aca="false">'Skill templates'!E6</f>
         <v>4</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="18" t="n">
         <f aca="false">'Skill templates'!F6</f>
         <v>2</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="18" t="n">
         <f aca="false">'Skill templates'!G6</f>
         <v>3</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="18" t="n">
         <f aca="false">'Skill templates'!H6</f>
         <v>3</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="18" t="n">
         <f aca="false">'Skill templates'!I6</f>
         <v>4</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="18" t="n">
         <f aca="false">'Skill templates'!J6</f>
         <v>3</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="18" t="n">
         <f aca="false">'Skill templates'!K6</f>
         <v>2</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="18" t="n">
         <f aca="false">'Skill templates'!L6</f>
         <v>2</v>
       </c>
-      <c r="N7" s="17" t="n">
+      <c r="N7" s="18" t="n">
         <f aca="false">'Skill templates'!M6</f>
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="17" t="n">
+      <c r="B8" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="18" t="n">
         <f aca="false">'Skill templates'!B6</f>
         <v>5</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <f aca="false">'Skill templates'!C6</f>
         <v>4</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">'Skill templates'!D6</f>
         <v>3</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <f aca="false">'Skill templates'!E6</f>
         <v>4</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <f aca="false">'Skill templates'!F6</f>
         <v>2</v>
       </c>
-      <c r="H8" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="17" t="n">
+      <c r="H8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="18" t="n">
         <f aca="false">'Skill templates'!H6</f>
         <v>3</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="18" t="n">
         <f aca="false">'Skill templates'!I6</f>
         <v>4</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="18" t="n">
         <f aca="false">'Skill templates'!J6</f>
         <v>3</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="18" t="n">
         <f aca="false">'Skill templates'!K6</f>
         <v>2</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="18" t="n">
         <f aca="false">'Skill templates'!L6</f>
         <v>2</v>
       </c>
-      <c r="N8" s="18" t="n">
+      <c r="N8" s="19" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" s="17" t="n">
+      <c r="B9" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="18" t="n">
         <f aca="false">'Skill templates'!D6</f>
         <v>3</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <f aca="false">'Skill templates'!E6</f>
         <v>4</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <f aca="false">'Skill templates'!F6</f>
         <v>2</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <f aca="false">'Skill templates'!G6</f>
         <v>3</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="18" t="n">
         <f aca="false">'Skill templates'!H6</f>
         <v>3</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <f aca="false">'Skill templates'!I6</f>
         <v>4</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="18" t="n">
         <f aca="false">'Skill templates'!J6</f>
         <v>3</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="18" t="n">
         <f aca="false">'Skill templates'!K6</f>
         <v>2</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="18" t="n">
         <f aca="false">'Skill templates'!L6</f>
         <v>2</v>
       </c>
-      <c r="N9" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="N9" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="17" t="n">
+      <c r="B10" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="18" t="n">
         <f aca="false">'Skill templates'!B6</f>
         <v>5</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <f aca="false">'Skill templates'!C6</f>
         <v>4</v>
       </c>
-      <c r="E10" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="17" t="n">
+      <c r="E10" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="18" t="n">
         <f aca="false">'Skill templates'!E6</f>
         <v>4</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <f aca="false">'Skill templates'!F6</f>
         <v>2</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <f aca="false">'Skill templates'!G6</f>
         <v>3</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <f aca="false">'Skill templates'!H6</f>
         <v>3</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="18" t="n">
         <f aca="false">'Skill templates'!I6</f>
         <v>4</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="18" t="n">
         <f aca="false">'Skill templates'!J6</f>
         <v>3</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="18" t="n">
         <f aca="false">'Skill templates'!K6</f>
         <v>2</v>
       </c>
-      <c r="M10" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="M10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="17" t="n">
+      <c r="B11" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="18" t="n">
         <f aca="false">'Skill templates'!B7</f>
         <v>4</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">'Skill templates'!D7</f>
         <v>2</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <f aca="false">'Skill templates'!E7</f>
         <v>2</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <f aca="false">'Skill templates'!F7</f>
         <v>2</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="I11" s="18" t="n">
         <f aca="false">'Skill templates'!H7</f>
         <v>3</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="18" t="n">
         <f aca="false">'Skill templates'!I7</f>
         <v>3</v>
       </c>
-      <c r="K11" s="17" t="n">
+      <c r="K11" s="18" t="n">
         <f aca="false">'Skill templates'!J7</f>
         <v>5</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="18" t="n">
         <f aca="false">'Skill templates'!K7</f>
         <v>3</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="18" t="n">
         <f aca="false">'Skill templates'!L7</f>
         <v>2</v>
       </c>
-      <c r="N11" s="17" t="n">
+      <c r="N11" s="18" t="n">
         <f aca="false">'Skill templates'!M7</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="17" t="n">
+      <c r="B12" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="18" t="n">
         <f aca="false">'Skill templates'!B7</f>
         <v>4</v>
       </c>
-      <c r="D12" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" s="17" t="n">
+      <c r="D12" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <f aca="false">'Skill templates'!D7</f>
         <v>2</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <f aca="false">'Skill templates'!E7</f>
         <v>2</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <f aca="false">'Skill templates'!F7</f>
         <v>2</v>
       </c>
-      <c r="H12" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="18" t="n">
+      <c r="H12" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="18" t="n">
         <f aca="false">'Skill templates'!I7</f>
         <v>3</v>
       </c>
-      <c r="K12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="17" t="n">
+      <c r="K12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="18" t="n">
         <f aca="false">'Skill templates'!K7</f>
         <v>3</v>
       </c>
-      <c r="M12" s="17" t="n">
+      <c r="M12" s="18" t="n">
         <f aca="false">'Skill templates'!L7</f>
         <v>2</v>
       </c>
-      <c r="N12" s="17" t="n">
+      <c r="N12" s="18" t="n">
         <f aca="false">'Skill templates'!M7</f>
         <v>4</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="18" t="n">
+      <c r="B13" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">'Skill templates'!D7</f>
         <v>2</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <f aca="false">'Skill templates'!E7</f>
         <v>2</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <f aca="false">'Skill templates'!F7</f>
         <v>2</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <f aca="false">'Skill templates'!G7</f>
         <v>5</v>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="18" t="n">
         <f aca="false">'Skill templates'!H7</f>
         <v>3</v>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="18" t="n">
         <f aca="false">'Skill templates'!I7</f>
         <v>3</v>
       </c>
-      <c r="K13" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" s="17" t="n">
+      <c r="K13" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" s="18" t="n">
         <f aca="false">'Skill templates'!K7</f>
         <v>3</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M13" s="18" t="n">
         <f aca="false">'Skill templates'!L7</f>
         <v>2</v>
       </c>
-      <c r="N13" s="17" t="n">
+      <c r="N13" s="18" t="n">
         <f aca="false">'Skill templates'!M7</f>
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="17" t="n">
+      <c r="B14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="18" t="n">
         <f aca="false">'Skill templates'!B7</f>
         <v>4</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">'Skill templates'!C7</f>
         <v>8</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">'Skill templates'!D7</f>
         <v>2</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <f aca="false">'Skill templates'!E7</f>
         <v>2</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <f aca="false">'Skill templates'!F7</f>
         <v>2</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I14" s="18" t="n">
         <f aca="false">'Skill templates'!H7</f>
         <v>3</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="18" t="n">
         <f aca="false">'Skill templates'!I7</f>
         <v>3</v>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="K14" s="18" t="n">
         <f aca="false">'Skill templates'!J7</f>
         <v>5</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="18" t="n">
         <f aca="false">'Skill templates'!K7</f>
         <v>3</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="18" t="n">
         <f aca="false">'Skill templates'!L7</f>
         <v>2</v>
       </c>
-      <c r="N14" s="18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+      <c r="N14" s="19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="17" t="n">
+      <c r="B15" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="18" t="n">
         <f aca="false">'Skill templates'!B9</f>
         <v>2</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <f aca="false">'Skill templates'!C9</f>
         <v>3</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">'Skill templates'!D9</f>
         <v>4</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="18" t="n">
         <f aca="false">'Skill templates'!E9</f>
         <v>3</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <f aca="false">'Skill templates'!F9</f>
         <v>3</v>
       </c>
-      <c r="H15" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="17" t="n">
+      <c r="H15" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="18" t="n">
         <f aca="false">'Skill templates'!I9</f>
         <v>5</v>
       </c>
-      <c r="K15" s="17" t="n">
+      <c r="K15" s="18" t="n">
         <f aca="false">'Skill templates'!J9</f>
         <v>5</v>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L15" s="18" t="n">
         <f aca="false">'Skill templates'!K9</f>
         <v>8</v>
       </c>
-      <c r="M15" s="17" t="n">
+      <c r="M15" s="18" t="n">
         <f aca="false">'Skill templates'!L9</f>
         <v>6</v>
       </c>
-      <c r="N15" s="17" t="n">
+      <c r="N15" s="18" t="n">
         <f aca="false">'Skill templates'!M9</f>
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="17" t="n">
+      <c r="B16" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="18" t="n">
         <f aca="false">'Skill templates'!B9</f>
         <v>2</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <f aca="false">'Skill templates'!C9</f>
         <v>3</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">'Skill templates'!D9</f>
         <v>4</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="18" t="n">
         <f aca="false">'Skill templates'!E9</f>
         <v>3</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <f aca="false">'Skill templates'!F9</f>
         <v>3</v>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="18" t="n">
         <f aca="false">'Skill templates'!G9</f>
         <v>5</v>
       </c>
-      <c r="I16" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="18" t="n">
+      <c r="I16" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="K16" s="17" t="n">
+      <c r="K16" s="18" t="n">
         <f aca="false">'Skill templates'!J9</f>
         <v>5</v>
       </c>
-      <c r="L16" s="18" t="n">
+      <c r="L16" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M16" s="17" t="n">
+      <c r="M16" s="18" t="n">
         <f aca="false">'Skill templates'!L9</f>
         <v>6</v>
       </c>
-      <c r="N16" s="17" t="n">
+      <c r="N16" s="18" t="n">
         <f aca="false">'Skill templates'!M9</f>
         <v>4</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="17" t="n">
+      <c r="B17" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="18" t="n">
         <f aca="false">'Skill templates'!B9</f>
         <v>2</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">'Skill templates'!C9</f>
         <v>3</v>
       </c>
-      <c r="E17" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="17" t="n">
+      <c r="E17" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="18" t="n">
         <f aca="false">'Skill templates'!E9</f>
         <v>3</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <f aca="false">'Skill templates'!F9</f>
         <v>3</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="18" t="n">
         <f aca="false">'Skill templates'!G9</f>
         <v>5</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="18" t="n">
         <f aca="false">'Skill templates'!H9</f>
         <v>4</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="18" t="n">
         <f aca="false">'Skill templates'!I9</f>
         <v>5</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="18" t="n">
         <f aca="false">'Skill templates'!J9</f>
         <v>5</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="18" t="n">
         <f aca="false">'Skill templates'!K9</f>
         <v>8</v>
       </c>
-      <c r="M17" s="18" t="n">
+      <c r="M17" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N17" s="17" t="n">
+      <c r="N17" s="18" t="n">
         <f aca="false">'Skill templates'!M9</f>
         <v>4</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="17" t="n">
+      <c r="B18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="18" t="n">
         <f aca="false">'Skill templates'!B8</f>
         <v>3</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">'Skill templates'!C8</f>
         <v>2</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <f aca="false">'Skill templates'!D8</f>
         <v>8</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="18" t="n">
         <f aca="false">'Skill templates'!E8</f>
         <v>7</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="18" t="n">
         <f aca="false">'Skill templates'!F8</f>
         <v>6</v>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="H18" s="18" t="n">
         <f aca="false">'Skill templates'!G8</f>
         <v>3</v>
       </c>
-      <c r="I18" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="17" t="n">
+      <c r="I18" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" s="18" t="n">
         <f aca="false">'Skill templates'!I8</f>
         <v>6</v>
       </c>
-      <c r="K18" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" s="17" t="n">
+      <c r="K18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="18" t="n">
         <f aca="false">'Skill templates'!K8</f>
         <v>2</v>
       </c>
-      <c r="M18" s="17" t="n">
+      <c r="M18" s="18" t="n">
         <f aca="false">'Skill templates'!L8</f>
         <v>3</v>
       </c>
-      <c r="N18" s="17" t="n">
+      <c r="N18" s="18" t="n">
         <f aca="false">'Skill templates'!M8</f>
         <v>3</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="17" t="n">
+      <c r="B19" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="18" t="n">
         <f aca="false">'Skill templates'!B8</f>
         <v>3</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <f aca="false">'Skill templates'!C8</f>
         <v>2</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="18" t="n">
         <f aca="false">'Skill templates'!F8</f>
         <v>6</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="18" t="n">
         <f aca="false">'Skill templates'!G8</f>
         <v>3</v>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I19" s="18" t="n">
         <f aca="false">'Skill templates'!H8</f>
         <v>6</v>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="18" t="n">
         <f aca="false">'Skill templates'!I8</f>
         <v>6</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="K19" s="18" t="n">
         <f aca="false">'Skill templates'!J8</f>
         <v>3</v>
       </c>
-      <c r="L19" s="17" t="n">
+      <c r="L19" s="18" t="n">
         <f aca="false">'Skill templates'!K8</f>
         <v>2</v>
       </c>
-      <c r="M19" s="17" t="n">
+      <c r="M19" s="18" t="n">
         <f aca="false">'Skill templates'!L8</f>
         <v>3</v>
       </c>
-      <c r="N19" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+      <c r="N19" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="17" t="n">
+      <c r="B20" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="18" t="n">
         <f aca="false">'Skill templates'!B8</f>
         <v>3</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">'Skill templates'!C8</f>
         <v>2</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="18" t="n">
         <f aca="false">'Skill templates'!D8</f>
         <v>8</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="18" t="n">
         <f aca="false">'Skill templates'!E8</f>
         <v>7</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="H20" s="17" t="n">
+      <c r="H20" s="18" t="n">
         <f aca="false">'Skill templates'!G8</f>
         <v>3</v>
       </c>
-      <c r="I20" s="17" t="n">
+      <c r="I20" s="18" t="n">
         <f aca="false">'Skill templates'!H8</f>
         <v>6</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="18" t="n">
         <f aca="false">'Skill templates'!I8</f>
         <v>6</v>
       </c>
-      <c r="K20" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" s="17" t="n">
+      <c r="K20" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" s="18" t="n">
         <f aca="false">'Skill templates'!K8</f>
         <v>2</v>
       </c>
-      <c r="M20" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" s="17" t="n">
+      <c r="M20" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" s="18" t="n">
         <f aca="false">'Skill templates'!M8</f>
         <v>3</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="17" t="n">
+      <c r="B21" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="18" t="n">
         <f aca="false">'Skill templates'!B10</f>
         <v>5</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">'Skill templates'!C10</f>
         <v>5</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="18" t="n">
         <f aca="false">'Skill templates'!D10</f>
         <v>5</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="18" t="n">
         <f aca="false">'Skill templates'!E10</f>
         <v>5</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="18" t="n">
         <f aca="false">'Skill templates'!F10</f>
         <v>5</v>
       </c>
-      <c r="H21" s="17" t="n">
+      <c r="H21" s="18" t="n">
         <f aca="false">'Skill templates'!G10</f>
         <v>5</v>
       </c>
-      <c r="I21" s="17" t="n">
+      <c r="I21" s="18" t="n">
         <f aca="false">'Skill templates'!H10</f>
         <v>5</v>
       </c>
-      <c r="J21" s="17" t="n">
+      <c r="J21" s="18" t="n">
         <f aca="false">'Skill templates'!I10</f>
         <v>5</v>
       </c>
-      <c r="K21" s="17" t="n">
+      <c r="K21" s="18" t="n">
         <f aca="false">'Skill templates'!J10</f>
         <v>5</v>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="18" t="n">
         <f aca="false">'Skill templates'!K10</f>
         <v>5</v>
       </c>
-      <c r="M21" s="17" t="n">
+      <c r="M21" s="18" t="n">
         <f aca="false">'Skill templates'!L10</f>
         <v>5</v>
       </c>
-      <c r="N21" s="17" t="n">
+      <c r="N21" s="18" t="n">
         <f aca="false">'Skill templates'!M10</f>
         <v>5</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>91</v>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <f aca="false">'Skill templates'!B5</f>
+        <v>3</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <f aca="false">'Skill templates'!C5</f>
+        <v>3</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <f aca="false">'Skill templates'!D5</f>
+        <v>2</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <f aca="false">'Skill templates'!E5</f>
+        <v>1</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <f aca="false">'Skill templates'!F5</f>
+        <v>1</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <f aca="false">'Skill templates'!G5</f>
+        <v>1</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <f aca="false">'Skill templates'!H5</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <f aca="false">'Skill templates'!I5</f>
+        <v>1</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <f aca="false">'Skill templates'!J5</f>
+        <v>1</v>
+      </c>
+      <c r="L22" s="18" t="n">
+        <f aca="false">'Skill templates'!K5</f>
+        <v>1</v>
+      </c>
+      <c r="M22" s="18" t="n">
+        <f aca="false">'Skill templates'!L5</f>
+        <v>1</v>
+      </c>
+      <c r="N22" s="18" t="n">
+        <f aca="false">'Skill templates'!M5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3436,1085 +3552,1143 @@
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="5" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="J5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="K5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="N5" s="5" t="s">
+      <c r="M5" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="str">
+      <c r="N5" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="str">
         <f aca="false">Attributes!A5</f>
         <v>Human Peasant (ref)</v>
       </c>
-      <c r="B6" s="17" t="str">
+      <c r="B6" s="18" t="str">
         <f aca="false">Attributes!P5</f>
         <v>Melee</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C5+FLOOR((Attributes!E5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D5+FLOOR((Attributes!E5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E5+FLOOR((Attributes!K5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F5+FLOOR((Attributes!F5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G5+FLOOR((Attributes!F5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H5+FLOOR((Attributes!F5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I5+FLOOR((Attributes!J5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J5+FLOOR((Attributes!K5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K5+FLOOR((Attributes!J5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L5+FLOOR((Attributes!I5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M5+FLOOR((Attributes!I5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N5+FLOOR((Attributes!L5-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="str">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="str">
         <f aca="false">Attributes!A6</f>
         <v>Skeleton Worker</v>
       </c>
-      <c r="B7" s="17" t="str">
+      <c r="B7" s="18" t="str">
         <f aca="false">Attributes!P6</f>
         <v>Melee</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C6+FLOOR((Attributes!E6-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D6+FLOOR((Attributes!E6-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E6+FLOOR((Attributes!K6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F6+FLOOR((Attributes!F6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G6+FLOOR((Attributes!F6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H6+FLOOR((Attributes!F6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I6+FLOOR((Attributes!J6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J6+FLOOR((Attributes!K6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K6+FLOOR((Attributes!J6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L6+FLOOR((Attributes!I6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M6+FLOOR((Attributes!I6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="N7" s="12" t="n">
+      <c r="N7" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N6+FLOOR((Attributes!L6-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="str">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="str">
         <f aca="false">Attributes!A7</f>
         <v>Orc</v>
       </c>
-      <c r="B8" s="17" t="str">
+      <c r="B8" s="18" t="str">
         <f aca="false">Attributes!P7</f>
         <v>Melee</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C7+FLOOR((Attributes!E7-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D7+FLOOR((Attributes!E7-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E7+FLOOR((Attributes!K7-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F7+FLOOR((Attributes!F7-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G7+FLOOR((Attributes!F7-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H7+FLOOR((Attributes!F7-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I7+FLOOR((Attributes!J7-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J7+FLOOR((Attributes!K7-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="K8" s="12" t="n">
+      <c r="K8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K7+FLOOR((Attributes!J7-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L7+FLOOR((Attributes!I7-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M7+FLOOR((Attributes!I7-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="N8" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N7+FLOOR((Attributes!L7-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="str">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="str">
         <f aca="false">Attributes!A8</f>
         <v>Hobgoblin</v>
       </c>
-      <c r="B9" s="17" t="str">
+      <c r="B9" s="18" t="str">
         <f aca="false">Attributes!P8</f>
         <v>Melee</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C8+FLOOR((Attributes!E8-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D8+FLOOR((Attributes!E8-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E8+FLOOR((Attributes!K8-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F8+FLOOR((Attributes!F8-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G8+FLOOR((Attributes!F8-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H8+FLOOR((Attributes!F8-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I8+FLOOR((Attributes!J8-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J8+FLOOR((Attributes!K8-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="K9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K8+FLOOR((Attributes!J8-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L8+FLOOR((Attributes!I8-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M8+FLOOR((Attributes!I8-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="N9" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N8+FLOOR((Attributes!L8-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="str">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="str">
         <f aca="false">Attributes!A9</f>
         <v>Ogre</v>
       </c>
-      <c r="B10" s="17" t="str">
+      <c r="B10" s="18" t="str">
         <f aca="false">Attributes!P9</f>
         <v>Melee</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C9+FLOOR((Attributes!E9-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D9+FLOOR((Attributes!E9-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E9+FLOOR((Attributes!K9-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F9+FLOOR((Attributes!F9-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G9+FLOOR((Attributes!F9-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H9+FLOOR((Attributes!F9-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I9+FLOOR((Attributes!J9-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J9+FLOOR((Attributes!K9-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K9+FLOOR((Attributes!J9-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="L10" s="12" t="n">
+      <c r="L10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L9+FLOOR((Attributes!I9-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M9+FLOOR((Attributes!I9-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N9+FLOOR((Attributes!L9-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="str">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="str">
         <f aca="false">Attributes!A10</f>
         <v>Troll</v>
       </c>
-      <c r="B11" s="17" t="str">
+      <c r="B11" s="18" t="str">
         <f aca="false">Attributes!P10</f>
         <v>Melee</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C10+FLOOR((Attributes!E10-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D10+FLOOR((Attributes!E10-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E10+FLOOR((Attributes!K10-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F10+FLOOR((Attributes!F10-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G10+FLOOR((Attributes!F10-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H10+FLOOR((Attributes!F10-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I10+FLOOR((Attributes!J10-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J10+FLOOR((Attributes!K10-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K10+FLOOR((Attributes!J10-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="L11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L10+FLOOR((Attributes!I10-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M10+FLOOR((Attributes!I10-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N10+FLOOR((Attributes!L10-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="str">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="str">
         <f aca="false">Attributes!A11</f>
         <v>Gray Dwarf</v>
       </c>
-      <c r="B12" s="17" t="str">
+      <c r="B12" s="18" t="str">
         <f aca="false">Attributes!P11</f>
         <v>Melee</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C11+FLOOR((Attributes!E11-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D11+FLOOR((Attributes!E11-5)/$B$3,1)))</f>
         <v>9</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E11+FLOOR((Attributes!K11-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F11+FLOOR((Attributes!F11-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G11+FLOOR((Attributes!F11-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H11+FLOOR((Attributes!F11-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I11+FLOOR((Attributes!J11-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="J12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J11+FLOOR((Attributes!K11-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="K12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K11+FLOOR((Attributes!J11-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L11+FLOOR((Attributes!I11-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="M12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M11+FLOOR((Attributes!I11-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="N12" s="12" t="n">
+      <c r="N12" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N11+FLOOR((Attributes!L11-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="str">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="str">
         <f aca="false">Attributes!A12</f>
         <v>Kobold</v>
       </c>
-      <c r="B13" s="17" t="str">
+      <c r="B13" s="18" t="str">
         <f aca="false">Attributes!P12</f>
         <v>Ranged</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C12+FLOOR((Attributes!E12-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D12+FLOOR((Attributes!E12-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E12+FLOOR((Attributes!K12-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F12+FLOOR((Attributes!F12-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G12+FLOOR((Attributes!F12-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H12+FLOOR((Attributes!F12-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I12+FLOOR((Attributes!J12-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J12+FLOOR((Attributes!K12-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="K13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K12+FLOOR((Attributes!J12-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="L13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L12+FLOOR((Attributes!I12-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M12+FLOOR((Attributes!I12-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="N13" s="12" t="n">
+      <c r="N13" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N12+FLOOR((Attributes!L12-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="str">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="str">
         <f aca="false">Attributes!A13</f>
         <v>Minotaur</v>
       </c>
-      <c r="B14" s="17" t="str">
+      <c r="B14" s="18" t="str">
         <f aca="false">Attributes!P13</f>
         <v>Melee</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C13+FLOOR((Attributes!E13-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D13+FLOOR((Attributes!E13-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E13+FLOOR((Attributes!K13-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F13+FLOOR((Attributes!F13-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G13+FLOOR((Attributes!F13-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H13+FLOOR((Attributes!F13-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I13+FLOOR((Attributes!J13-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J13+FLOOR((Attributes!K13-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="K14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K13+FLOOR((Attributes!J13-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L13+FLOOR((Attributes!I13-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="M14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M13+FLOOR((Attributes!I13-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="N14" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N13+FLOOR((Attributes!L13-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="str">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="str">
         <f aca="false">Attributes!A14</f>
         <v>Mountain Dwarf</v>
       </c>
-      <c r="B15" s="17" t="str">
+      <c r="B15" s="18" t="str">
         <f aca="false">Attributes!P14</f>
         <v>Melee</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C14+FLOOR((Attributes!E14-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D14+FLOOR((Attributes!E14-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E14+FLOOR((Attributes!K14-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F14+FLOOR((Attributes!F14-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G14+FLOOR((Attributes!F14-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H14+FLOOR((Attributes!F14-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I14+FLOOR((Attributes!J14-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J14+FLOOR((Attributes!K14-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="K15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K14+FLOOR((Attributes!J14-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="L15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L14+FLOOR((Attributes!I14-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M14+FLOOR((Attributes!I14-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="N15" s="12" t="n">
+      <c r="N15" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N14+FLOOR((Attributes!L14-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="str">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="str">
         <f aca="false">Attributes!A15</f>
         <v>Gnome</v>
       </c>
-      <c r="B16" s="17" t="str">
+      <c r="B16" s="18" t="str">
         <f aca="false">Attributes!P15</f>
         <v>Arcane</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C15+FLOOR((Attributes!E15-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D15+FLOOR((Attributes!E15-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E15+FLOOR((Attributes!K15-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F15+FLOOR((Attributes!F15-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G15+FLOOR((Attributes!F15-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H15+FLOOR((Attributes!F15-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I15+FLOOR((Attributes!J15-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J15+FLOOR((Attributes!K15-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K15+FLOOR((Attributes!J15-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="L16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L15+FLOOR((Attributes!I15-5)/$B$3,1)))</f>
         <v>9</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="M16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M15+FLOOR((Attributes!I15-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="N16" s="12" t="n">
+      <c r="N16" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N15+FLOOR((Attributes!L15-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="str">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="str">
         <f aca="false">Attributes!A16</f>
         <v>Dark Elf</v>
       </c>
-      <c r="B17" s="17" t="str">
+      <c r="B17" s="18" t="str">
         <f aca="false">Attributes!P16</f>
         <v>Ranged</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C16+FLOOR((Attributes!E16-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D16+FLOOR((Attributes!E16-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E16+FLOOR((Attributes!K16-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F16+FLOOR((Attributes!F16-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G16+FLOOR((Attributes!F16-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H16+FLOOR((Attributes!F16-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="I17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I16+FLOOR((Attributes!J16-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J16+FLOOR((Attributes!K16-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="K17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K16+FLOOR((Attributes!J16-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="L17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L16+FLOOR((Attributes!I16-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M16+FLOOR((Attributes!I16-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N16+FLOOR((Attributes!L16-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="str">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="str">
         <f aca="false">Attributes!A17</f>
         <v>High Elf</v>
       </c>
-      <c r="B18" s="17" t="str">
+      <c r="B18" s="18" t="str">
         <f aca="false">Attributes!P17</f>
         <v>Arcane</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C17+FLOOR((Attributes!E17-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D17+FLOOR((Attributes!E17-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E17+FLOOR((Attributes!K17-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F17+FLOOR((Attributes!F17-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G17+FLOOR((Attributes!F17-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H17+FLOOR((Attributes!F17-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I17+FLOOR((Attributes!J17-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J17+FLOOR((Attributes!K17-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="K18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K17+FLOOR((Attributes!J17-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="L18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L17+FLOOR((Attributes!I17-5)/$B$3,1)))</f>
         <v>9</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="M18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M17+FLOOR((Attributes!I17-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="N18" s="12" t="n">
+      <c r="N18" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N17+FLOOR((Attributes!L17-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="str">
         <f aca="false">Attributes!A18</f>
         <v>Goblin</v>
       </c>
-      <c r="B19" s="17" t="str">
+      <c r="B19" s="18" t="str">
         <f aca="false">Attributes!P18</f>
         <v>Ranged</v>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C18+FLOOR((Attributes!E18-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D18+FLOOR((Attributes!E18-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E18+FLOOR((Attributes!K18-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F18+FLOOR((Attributes!F18-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G18+FLOOR((Attributes!F18-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="H19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H18+FLOOR((Attributes!F18-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I18+FLOOR((Attributes!J18-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="J19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J18+FLOOR((Attributes!K18-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="K19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K18+FLOOR((Attributes!J18-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L18+FLOOR((Attributes!I18-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M18+FLOOR((Attributes!I18-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="N19" s="12" t="n">
+      <c r="N19" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N18+FLOOR((Attributes!L18-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="str">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="str">
         <f aca="false">Attributes!A19</f>
         <v>Gnoll</v>
       </c>
-      <c r="B20" s="17" t="str">
+      <c r="B20" s="18" t="str">
         <f aca="false">Attributes!P19</f>
         <v>Ranged</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C19+FLOOR((Attributes!E19-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D19+FLOOR((Attributes!E19-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E19+FLOOR((Attributes!K19-5)/$B$3,1)))</f>
         <v>10</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F19+FLOOR((Attributes!F19-5)/$B$3,1)))</f>
         <v>8</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G19+FLOOR((Attributes!F19-5)/$B$3,1)))</f>
         <v>6</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H19+FLOOR((Attributes!F19-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="I20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I19+FLOOR((Attributes!J19-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="J20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J19+FLOOR((Attributes!K19-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="K20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K19+FLOOR((Attributes!J19-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L19+FLOOR((Attributes!I19-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M19+FLOOR((Attributes!I19-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="N20" s="12" t="n">
+      <c r="N20" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N19+FLOOR((Attributes!L19-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="str">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="str">
         <f aca="false">Attributes!A20</f>
         <v>Halfling</v>
       </c>
-      <c r="B21" s="17" t="str">
+      <c r="B21" s="18" t="str">
         <f aca="false">Attributes!P20</f>
         <v>Ranged</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C20+FLOOR((Attributes!E20-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D20+FLOOR((Attributes!E20-5)/$B$3,1)))</f>
         <v>1</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E20+FLOOR((Attributes!K20-5)/$B$3,1)))</f>
         <v>9</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F20+FLOOR((Attributes!F20-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G20+FLOOR((Attributes!F20-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="H21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H20+FLOOR((Attributes!F20-5)/$B$3,1)))</f>
         <v>3</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I20+FLOOR((Attributes!J20-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J20+FLOOR((Attributes!K20-5)/$B$3,1)))</f>
         <v>7</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="K21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K20+FLOOR((Attributes!J20-5)/$B$3,1)))</f>
         <v>4</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L20+FLOOR((Attributes!I20-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="M21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M20+FLOOR((Attributes!I20-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="N21" s="12" t="n">
+      <c r="N21" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N20+FLOOR((Attributes!L20-5)/$B$3,1)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="str">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="str">
         <f aca="false">Attributes!A21</f>
         <v>Human Outcast</v>
       </c>
-      <c r="B22" s="17" t="str">
+      <c r="B22" s="18" t="str">
         <f aca="false">Attributes!P21</f>
         <v>Melee</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!C21+FLOOR((Attributes!E21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!D21+FLOOR((Attributes!E21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!E21+FLOOR((Attributes!K21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!F21+FLOOR((Attributes!F21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!G21+FLOOR((Attributes!F21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="H22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!H21+FLOOR((Attributes!F21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!I21+FLOOR((Attributes!J21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="J22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!J21+FLOOR((Attributes!K21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="K22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!K21+FLOOR((Attributes!J21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="L22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!L21+FLOOR((Attributes!I21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="M22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!M21+FLOOR((Attributes!I21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
-      <c r="N22" s="12" t="n">
+      <c r="N22" s="13" t="n">
         <f aca="false">MAX(1,MIN(10,'Race skills'!N21+FLOOR((Attributes!L21-5)/$B$3,1)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="str">
+        <f aca="false">Attributes!A22</f>
+        <v>Ghoul</v>
+      </c>
+      <c r="B23" s="18" t="str">
+        <f aca="false">Attributes!P22</f>
+        <v>Melee</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!C22+FLOOR((Attributes!E22-5)/$B$3,1)))</f>
+        <v>4</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!D22+FLOOR((Attributes!E22-5)/$B$3,1)))</f>
+        <v>4</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!E22+FLOOR((Attributes!K22-5)/$B$3,1)))</f>
+        <v>2</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!F22+FLOOR((Attributes!F22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!G22+FLOOR((Attributes!F22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!H22+FLOOR((Attributes!F22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!I22+FLOOR((Attributes!J22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!J22+FLOOR((Attributes!K22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!K22+FLOOR((Attributes!J22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!L22+FLOOR((Attributes!I22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!M22+FLOOR((Attributes!I22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <f aca="false">MAX(1,MIN(10,'Race skills'!N22+FLOOR((Attributes!L22-5)/$B$3,1)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -4536,159 +4710,159 @@
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="95"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="B3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="14" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="14" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="14" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="14" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="14" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="B8" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="B10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="14" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B12" s="14" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="B12" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B13" s="14" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B14" s="14" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="B14" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+      <c r="B17" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="14" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="B18" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="14" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="B19" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="14" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="B20" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="14" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
         <v>135</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
